--- a/German Bundesliga/Raw/24_25.xlsx
+++ b/German Bundesliga/Raw/24_25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Value_Betting_Projekt\German Bundesliga\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1D2D36-B2CC-4822-BE0A-EBE67D0D6831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856633E3-B549-4C16-B021-145D30C3DC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="161">
   <si>
     <t>Dato</t>
   </si>
@@ -16360,6 +16360,9 @@
       <c r="A122" t="s">
         <v>103</v>
       </c>
+      <c r="B122" t="s">
+        <v>43</v>
+      </c>
       <c r="C122" t="s">
         <v>52</v>
       </c>
@@ -16422,6 +16425,9 @@
       </c>
       <c r="W122" t="s">
         <v>58</v>
+      </c>
+      <c r="X122">
+        <v>2</v>
       </c>
       <c r="Y122">
         <v>13</v>
